--- a/argus/kship/models/059270_model.xlsx
+++ b/argus/kship/models/059270_model.xlsx
@@ -672,37 +672,37 @@
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 261026억 × 비례계수 0.0011 × 계절비중 Q3 0.237(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.77, n=14, 창 19)</t>
+고객지수 4분기 이동합(t−2) 261025억 × 비례계수 0.0011 × 계절비중 Q3 0.237(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.77, n=14, 창 19)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 262360억 × 비례계수 0.0011 × 계절비중 Q4 0.253(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.77, n=14, 창 19)</t>
+고객지수 4분기 이동합(t−2) 263179억 × 비례계수 0.0011 × 계절비중 Q4 0.253(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.77, n=14, 창 19)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 261074억 × 비례계수 0.0011 × 계절비중 Q1 0.228(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.77, n=14, 창 19)</t>
+고객지수 4분기 이동합(t−2) 261873억 × 비례계수 0.0011 × 계절비중 Q1 0.228(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.77, n=14, 창 19)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 258876억 × 비례계수 0.0011 × 계절비중 Q2 0.283(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.77, n=14, 창 19)</t>
+고객지수 4분기 이동합(t−2) 259656억 × 비례계수 0.0011 × 계절비중 Q2 0.283(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.77, n=14, 창 19)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 256251억 × 비례계수 0.0011 × 계절비중 Q3 0.237(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.77, n=14, 창 19)</t>
+고객지수 4분기 이동합(t−2) 257012억 × 비례계수 0.0011 × 계절비중 Q3 0.237(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.77, n=14, 창 19)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 253966억 × 비례계수 0.0011 × 계절비중 Q4 0.253(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.77, n=14, 창 19)</t>
+고객지수 4분기 이동합(t−2) 253887억 × 비례계수 0.0011 × 계절비중 Q4 0.253(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.77, n=14, 창 19)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1779,37 +1779,37 @@
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 261026억 × 비례계수 0.0011 × 계절비중 Q3 0.237(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.77, n=14, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−2) 261025억 × 비례계수 0.0011 × 계절비중 Q3 0.237(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.77, n=14, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 262360억 × 비례계수 0.0011 × 계절비중 Q4 0.253(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.77, n=14, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−2) 263179억 × 비례계수 0.0011 × 계절비중 Q4 0.253(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.77, n=14, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 261074억 × 비례계수 0.0011 × 계절비중 Q1 0.228(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.77, n=14, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−2) 261873억 × 비례계수 0.0011 × 계절비중 Q1 0.228(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.77, n=14, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 258876억 × 비례계수 0.0011 × 계절비중 Q2 0.283(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.77, n=14, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−2) 259656억 × 비례계수 0.0011 × 계절비중 Q2 0.283(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.77, n=14, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 256251억 × 비례계수 0.0011 × 계절비중 Q3 0.237(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.77, n=14, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−2) 257012억 × 비례계수 0.0011 × 계절비중 Q3 0.237(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.77, n=14, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 253966억 × 비례계수 0.0011 × 계절비중 Q4 0.253(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.77, n=14, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−2) 253887억 × 비례계수 0.0011 × 계절비중 Q4 0.253(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.77, n=14, 창 19)
 [yoy]</t>
       </text>
     </comment>
@@ -6457,20 +6457,20 @@
         <v>0.326694</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.200099</v>
+        <v>0.20388</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.086075</v>
+        <v>0.08939800000000001</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.016919</v>
+        <v>0.020076</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>-0.018251</v>
+        <v>-0.015308</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>-0.031922</v>
+        <v>-0.035236</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -6606,23 +6606,23 @@
         <v>0.190168</v>
       </c>
       <c r="AI22" s="24" t="n">
-        <v>0.190163</v>
+        <v>0.190249</v>
       </c>
       <c r="AJ22" s="25">
         <f>IFERROR(subQ!AJ8/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK22" s="24" t="n">
-        <v>0.190177</v>
+        <v>0.190207</v>
       </c>
       <c r="AL22" s="24" t="n">
-        <v>0.190216</v>
+        <v>0.190123</v>
       </c>
       <c r="AM22" s="24" t="n">
-        <v>0.190105</v>
+        <v>0.190135</v>
       </c>
       <c r="AN22" s="24" t="n">
-        <v>0.190207</v>
+        <v>0.190119</v>
       </c>
       <c r="AO22" s="25">
         <f>IFERROR(subQ!AO8/subQ!AO5,"")</f>
@@ -6761,23 +6761,23 @@
         <v>-0.057845</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>-0.057953</v>
+        <v>-0.057908</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>-0.057834</v>
+        <v>-0.057962</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>-0.057859</v>
+        <v>-0.057928</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>-0.057871</v>
+        <v>-0.057848</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>-0.057883</v>
+        <v>-0.057899</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -7769,13 +7769,13 @@
         <v>0</v>
       </c>
       <c r="AL30" s="29" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AM30" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="AM30" s="29" t="n">
-        <v>-0.01</v>
-      </c>
       <c r="AN30" s="29" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO30" s="30" t="n"/>
     </row>
@@ -7897,13 +7897,13 @@
         <v>0</v>
       </c>
       <c r="AL31" s="29" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AM31" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="AM31" s="29" t="n">
-        <v>-0.01</v>
-      </c>
       <c r="AN31" s="29" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO31" s="30" t="n"/>
     </row>
@@ -8146,20 +8146,20 @@
         <v>-0.022243</v>
       </c>
       <c r="AI33" s="24" t="n">
-        <v>-0.025504</v>
+        <v>-0.025682</v>
       </c>
       <c r="AJ33" s="25" t="n"/>
       <c r="AK33" s="24" t="n">
-        <v>-0.022342</v>
+        <v>-0.022346</v>
       </c>
       <c r="AL33" s="24" t="n">
-        <v>-0.031154</v>
+        <v>-0.031346</v>
       </c>
       <c r="AM33" s="24" t="n">
-        <v>-0.02455</v>
+        <v>-0.024656</v>
       </c>
       <c r="AN33" s="24" t="n">
-        <v>-0.027734</v>
+        <v>-0.027649</v>
       </c>
       <c r="AO33" s="25" t="n"/>
     </row>
@@ -8274,20 +8274,20 @@
         <v>-0.011062</v>
       </c>
       <c r="AI34" s="24" t="n">
-        <v>-0.01254</v>
+        <v>-0.012584</v>
       </c>
       <c r="AJ34" s="25" t="n"/>
       <c r="AK34" s="24" t="n">
-        <v>-0.010797</v>
+        <v>-0.010886</v>
       </c>
       <c r="AL34" s="24" t="n">
-        <v>-0.014941</v>
+        <v>-0.014987</v>
       </c>
       <c r="AM34" s="24" t="n">
-        <v>-0.011625</v>
+        <v>-0.011673</v>
       </c>
       <c r="AN34" s="24" t="n">
-        <v>-0.012865</v>
+        <v>-0.012868</v>
       </c>
       <c r="AO34" s="25" t="n"/>
     </row>
@@ -9335,23 +9335,23 @@
         <v>-0.057845</v>
       </c>
       <c r="AI43" s="24" t="n">
-        <v>-0.057953</v>
+        <v>-0.057908</v>
       </c>
       <c r="AJ43" s="25">
         <f>IFERROR(subQ!AJ34/subQ!AJ33,"")</f>
         <v/>
       </c>
       <c r="AK43" s="24" t="n">
-        <v>-0.057834</v>
+        <v>-0.057962</v>
       </c>
       <c r="AL43" s="24" t="n">
-        <v>-0.057859</v>
+        <v>-0.057928</v>
       </c>
       <c r="AM43" s="24" t="n">
-        <v>-0.057871</v>
+        <v>-0.057848</v>
       </c>
       <c r="AN43" s="24" t="n">
-        <v>-0.057883</v>
+        <v>-0.057899</v>
       </c>
       <c r="AO43" s="25">
         <f>IFERROR(subQ!AO34/subQ!AO33,"")</f>

--- a/argus/kship/models/059270_model.xlsx
+++ b/argus/kship/models/059270_model.xlsx
@@ -666,43 +666,43 @@
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 254552억 × 비례계수 0.0011 × 계절비중 Q2 0.283(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.77, n=14, 창 19)</t>
+고객지수 4분기 이동합(t−2) 255541억 × 비례계수 0.0011 × 계절비중 Q2 0.283(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.77, n=14, 창 19)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 261025억 × 비례계수 0.0011 × 계절비중 Q3 0.237(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.77, n=14, 창 19)</t>
+고객지수 4분기 이동합(t−2) 265726억 × 비례계수 0.0011 × 계절비중 Q3 0.237(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.77, n=14, 창 19)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 263179억 × 비례계수 0.0011 × 계절비중 Q4 0.253(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.77, n=14, 창 19)</t>
+고객지수 4분기 이동합(t−2) 275679억 × 비례계수 0.0011 × 계절비중 Q4 0.253(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.77, n=14, 창 19)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 261873억 × 비례계수 0.0011 × 계절비중 Q1 0.228(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.77, n=14, 창 19)</t>
+고객지수 4분기 이동합(t−2) 287258억 × 비례계수 0.0011 × 계절비중 Q1 0.228(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.77, n=14, 창 19)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 259656억 × 비례계수 0.0011 × 계절비중 Q2 0.283(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.77, n=14, 창 19)</t>
+고객지수 4분기 이동합(t−2) 302650억 × 비례계수 0.0011 × 계절비중 Q2 0.283(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.77, n=14, 창 19)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 257012억 × 비례계수 0.0011 × 계절비중 Q3 0.237(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.77, n=14, 창 19)</t>
+고객지수 4분기 이동합(t−2) 320867억 × 비례계수 0.0011 × 계절비중 Q3 0.237(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.77, n=14, 창 19)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 253887억 × 비례계수 0.0011 × 계절비중 Q4 0.253(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.77, n=14, 창 19)</t>
+고객지수 4분기 이동합(t−2) 340383억 × 비례계수 0.0011 × 계절비중 Q4 0.253(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.77, n=14, 창 19)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -930,19 +930,19 @@
     <comment ref="AL25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 224억 × 2.37% − 총차입금 116억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 223억 × 2.37% − 총차입금 116억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AM25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 220억 × 2.37% − 총차입금 116억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 219억 × 2.37% − 총차입금 116억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AN25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 218억 × 2.37% − 총차입금 116억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 215억 × 2.37% − 총차입금 116억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AC26" authorId="0" shapeId="0">
@@ -1773,43 +1773,43 @@
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 254552억 × 비례계수 0.0011 × 계절비중 Q2 0.283(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.77, n=14, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−2) 255541억 × 비례계수 0.0011 × 계절비중 Q2 0.283(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.77, n=14, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 261025억 × 비례계수 0.0011 × 계절비중 Q3 0.237(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.77, n=14, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−2) 265726억 × 비례계수 0.0011 × 계절비중 Q3 0.237(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.77, n=14, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 263179억 × 비례계수 0.0011 × 계절비중 Q4 0.253(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.77, n=14, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−2) 275679억 × 비례계수 0.0011 × 계절비중 Q4 0.253(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.77, n=14, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 261873억 × 비례계수 0.0011 × 계절비중 Q1 0.228(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.77, n=14, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−2) 287258억 × 비례계수 0.0011 × 계절비중 Q1 0.228(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.77, n=14, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 259656억 × 비례계수 0.0011 × 계절비중 Q2 0.283(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.77, n=14, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−2) 302650억 × 비례계수 0.0011 × 계절비중 Q2 0.283(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.77, n=14, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 257012억 × 비례계수 0.0011 × 계절비중 Q3 0.237(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.77, n=14, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−2) 320867억 × 비례계수 0.0011 × 계절비중 Q3 0.237(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.77, n=14, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 253887억 × 비례계수 0.0011 × 계절비중 Q4 0.253(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.77, n=14, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−2) 340383억 × 비례계수 0.0011 × 계절비중 Q4 0.253(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.77, n=14, 창 19)
 [yoy]</t>
       </text>
     </comment>
@@ -2252,19 +2252,19 @@
     </comment>
     <comment ref="AL11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 224억 × 2.37% − 총차입금 116억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 223억 × 2.37% − 총차입금 116억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AM11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 220억 × 2.37% − 총차입금 116억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 219억 × 2.37% − 총차입금 116억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AN11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 218억 × 2.37% − 총차입금 116억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 215억 × 2.37% − 총차입금 116억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
@@ -4265,7 +4265,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-09-30</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-02</t>
         </is>
       </c>
     </row>
@@ -4393,7 +4393,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>백테스트: {"freeze": "2025Q2", "horizon": 4, "revenue_wape_pct": 14.0, "op_wape_pct": 60.1, "n": 4, "note": "단일 회사 4분기 — 통계 아님", "driver_at_freeze": "trend_seasonal", "frozen_inputs": "fin(연결/별도)·고객 조선사 모델·지주 자회사 모델은 2025Q2 까지의 분기만; 선표는 체결일 ≤ 2025Q2 말일 계약(원장 최신 금액·코호트 등급, 환산 없음); 잔고는 yards_cache 2025Q2; 시세·환율 forward·prices 미사용. 고객 가중치(suppliers.json 언급 비중)와 합병 체인링크는 현재 지식", "detail": [{"q": "2025Q3", "rev_pred": 33.32, "rev_act": 38.02, "op_pred": -2.52, "op_act": -0.27}, {"q": "2025Q4", "rev_pred": 35.25, "rev_act": 42.11, "op_pred": -2.67, "op_act": -2.29}, {"q": "2026Q1", "rev_pred": 30.03, "rev_act": 32.86, "op_pred": -2.27, "op_act": -3.04}, {"q": "2026Q2", "rev_pred": 39.2, "rev_act": 33.15, "op_pred": -2.97, "op_act": -7.36}]}</t>
+          <t>백테스트: {"freeze": "2025Q2", "horizon": 4, "revenue_wape_pct": 14.0, "op_wape_pct": 60.1, "n": 4, "note": "단일 회사 4분기 — 통계 아님", "driver_at_freeze": "trend_seasonal", "selection_oos_at_freeze": {"wape_link": null, "wape_trend": null, "adopted": false, "note": "유의성 조건 미달 → OOS 비교 전 기각"}, "frozen_inputs": "fin(연결/별도)·고객 조선사 모델·지주 자회사 모델은 2025Q2 까지의 분기만; 선표는 체결일 ≤ 2025Q2 말일 계약(원장 최신 금액·코호트 등급, 환산 없음); 잔고는 yards_cache 2025Q2; 시세·환율 forward·prices·forecast_panel 신규수주 미사용. 고객 가중치(suppliers.json 언급 비중)와 합병 체인링크는 현재 지식; 고객 연동 채택은 동결 모델 안에서도 자기 la−4분기 OOS 규칙(selection_oos_at_freeze)", "detail": [{"q": "2025Q3", "rev_pred": 33.32, "rev_act": 38.02, "op_pred": -2.52, "op_act": -0.27}, {"q": "2025Q4", "rev_pred": 35.25, "rev_act": 42.11, "op_pred": -2.67, "op_act": -2.29}, {"q": "2026Q1", "rev_pred": 30.03, "rev_act": 32.86, "op_pred": -2.27, "op_act": -3.04}, {"q": "2026Q2", "rev_pred": 39.2, "rev_act": 33.15, "op_pred": -2.97, "op_act": -7.36}]}</t>
         </is>
       </c>
     </row>
@@ -6451,26 +6451,26 @@
         <v>0.831668</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>1.388895</v>
+        <v>1.398246</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.326694</v>
+        <v>0.350517</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.20388</v>
+        <v>0.261098</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.08939800000000001</v>
+        <v>0.195081</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.020076</v>
+        <v>0.184254</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>-0.015308</v>
+        <v>0.207634</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>-0.035236</v>
+        <v>0.234681</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -6600,29 +6600,29 @@
         <v>0.190263</v>
       </c>
       <c r="AG22" s="24" t="n">
-        <v>0.190152</v>
+        <v>0.190165</v>
       </c>
       <c r="AH22" s="24" t="n">
-        <v>0.190168</v>
+        <v>0.190139</v>
       </c>
       <c r="AI22" s="24" t="n">
-        <v>0.190249</v>
+        <v>0.190222</v>
       </c>
       <c r="AJ22" s="25">
         <f>IFERROR(subQ!AJ8/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK22" s="24" t="n">
-        <v>0.190207</v>
+        <v>0.190211</v>
       </c>
       <c r="AL22" s="24" t="n">
-        <v>0.190123</v>
+        <v>0.190208</v>
       </c>
       <c r="AM22" s="24" t="n">
-        <v>0.190135</v>
+        <v>0.190134</v>
       </c>
       <c r="AN22" s="24" t="n">
-        <v>0.190119</v>
+        <v>0.19018</v>
       </c>
       <c r="AO22" s="25">
         <f>IFERROR(subQ!AO8/subQ!AO5,"")</f>
@@ -6755,29 +6755,29 @@
         <v>-0.057827</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>-0.057828</v>
+        <v>-0.057854</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>-0.057845</v>
+        <v>-0.057837</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>-0.057908</v>
+        <v>-0.057888</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>-0.057962</v>
+        <v>-0.057842</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>-0.057928</v>
+        <v>-0.05788</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>-0.057848</v>
+        <v>-0.05783</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>-0.057899</v>
+        <v>-0.057867</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -7051,7 +7051,7 @@
         <v>1.3</v>
       </c>
       <c r="AN25" s="29" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AO25" s="30">
         <f>subQ!AO11</f>
@@ -7762,14 +7762,14 @@
         <v>0</v>
       </c>
       <c r="AI30" s="29" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="AJ30" s="30" t="n"/>
       <c r="AK30" s="29" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="AL30" s="29" t="n">
         <v>0</v>
-      </c>
-      <c r="AL30" s="29" t="n">
-        <v>-0</v>
       </c>
       <c r="AM30" s="29" t="n">
         <v>0</v>
@@ -7890,14 +7890,14 @@
         <v>0</v>
       </c>
       <c r="AI31" s="29" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="AJ31" s="30" t="n"/>
       <c r="AK31" s="29" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="AL31" s="29" t="n">
         <v>0</v>
-      </c>
-      <c r="AL31" s="29" t="n">
-        <v>-0</v>
       </c>
       <c r="AM31" s="29" t="n">
         <v>0</v>
@@ -8140,26 +8140,26 @@
         <v>-0.017281</v>
       </c>
       <c r="AG33" s="24" t="n">
-        <v>-0.02697</v>
+        <v>-0.027139</v>
       </c>
       <c r="AH33" s="24" t="n">
-        <v>-0.022243</v>
+        <v>-0.022856</v>
       </c>
       <c r="AI33" s="24" t="n">
-        <v>-0.025682</v>
+        <v>-0.027481</v>
       </c>
       <c r="AJ33" s="25" t="n"/>
       <c r="AK33" s="24" t="n">
-        <v>-0.022346</v>
+        <v>-0.025789</v>
       </c>
       <c r="AL33" s="24" t="n">
-        <v>-0.031346</v>
+        <v>-0.038862</v>
       </c>
       <c r="AM33" s="24" t="n">
-        <v>-0.024656</v>
+        <v>-0.034476</v>
       </c>
       <c r="AN33" s="24" t="n">
-        <v>-0.027649</v>
+        <v>-0.042585</v>
       </c>
       <c r="AO33" s="25" t="n"/>
     </row>
@@ -8268,26 +8268,26 @@
         <v>-0.008787</v>
       </c>
       <c r="AG34" s="24" t="n">
-        <v>-0.013639</v>
+        <v>-0.013682</v>
       </c>
       <c r="AH34" s="24" t="n">
-        <v>-0.011062</v>
+        <v>-0.011408</v>
       </c>
       <c r="AI34" s="24" t="n">
-        <v>-0.012584</v>
+        <v>-0.013463</v>
       </c>
       <c r="AJ34" s="25" t="n"/>
       <c r="AK34" s="24" t="n">
-        <v>-0.010886</v>
+        <v>-0.012539</v>
       </c>
       <c r="AL34" s="24" t="n">
-        <v>-0.014987</v>
+        <v>-0.018532</v>
       </c>
       <c r="AM34" s="24" t="n">
-        <v>-0.011673</v>
+        <v>-0.016184</v>
       </c>
       <c r="AN34" s="24" t="n">
-        <v>-0.012868</v>
+        <v>-0.019518</v>
       </c>
       <c r="AO34" s="25" t="n"/>
     </row>
@@ -9041,10 +9041,10 @@
         <v>0.027211</v>
       </c>
       <c r="AM41" s="24" t="n">
-        <v>0.027027</v>
+        <v>0.033784</v>
       </c>
       <c r="AN41" s="24" t="n">
-        <v>0.026846</v>
+        <v>0.040268</v>
       </c>
       <c r="AO41" s="25" t="n"/>
     </row>
@@ -9329,29 +9329,29 @@
         <v>-0.057827</v>
       </c>
       <c r="AG43" s="24" t="n">
-        <v>-0.057828</v>
+        <v>-0.057854</v>
       </c>
       <c r="AH43" s="24" t="n">
-        <v>-0.057845</v>
+        <v>-0.057837</v>
       </c>
       <c r="AI43" s="24" t="n">
-        <v>-0.057908</v>
+        <v>-0.057888</v>
       </c>
       <c r="AJ43" s="25">
         <f>IFERROR(subQ!AJ34/subQ!AJ33,"")</f>
         <v/>
       </c>
       <c r="AK43" s="24" t="n">
-        <v>-0.057962</v>
+        <v>-0.057842</v>
       </c>
       <c r="AL43" s="24" t="n">
-        <v>-0.057928</v>
+        <v>-0.05788</v>
       </c>
       <c r="AM43" s="24" t="n">
-        <v>-0.057848</v>
+        <v>-0.05783</v>
       </c>
       <c r="AN43" s="24" t="n">
-        <v>-0.057899</v>
+        <v>-0.057867</v>
       </c>
       <c r="AO43" s="25">
         <f>IFERROR(subQ!AO34/subQ!AO33,"")</f>
@@ -10094,7 +10094,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-09-30</t>
+          <t>UPDATE: 26-10-02</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -10686,7 +10686,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-09-30</t>
+          <t>UPDATE: 26-10-02</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -30021,7 +30021,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>-79.90000000000001</v>
+        <v>-80.09999999999999</v>
       </c>
     </row>
     <row r="30">
@@ -30058,7 +30058,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>-0.0219</v>
+        <v>-0.022</v>
       </c>
     </row>
     <row r="34">

--- a/argus/kship/models/059270_model.xlsx
+++ b/argus/kship/models/059270_model.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="분기" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="TP" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="외화" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
@@ -4248,7 +4248,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-05</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-06</t>
         </is>
       </c>
     </row>
@@ -5119,35 +5119,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1354.78</v>
+        <v>1351.18</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1460.21</v>
+        <v>1459.61</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5238,35 +5238,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5357,35 +5357,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>858.4</v>
+        <v>855.39</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>921.0599999999999</v>
+        <v>920.6900000000001</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5476,35 +5476,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5595,35 +5595,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1525.7</v>
+        <v>1519.07</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1694.79</v>
+        <v>1693.81</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5714,35 +5714,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5833,35 +5833,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>202.07</v>
+        <v>201.53</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>214.1</v>
+        <v>214.03</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5952,35 +5952,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6087,7 +6087,7 @@
         <v>5460</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>5490</v>
+        <v>5480</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6360,7 +6360,7 @@
         <v>5525.9</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>5510</v>
+        <v>5500</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -9041,7 +9041,7 @@
         </is>
       </c>
       <c r="D42" s="34" t="n">
-        <v>5490</v>
+        <v>5480</v>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
@@ -9081,7 +9081,7 @@
       </c>
       <c r="D43" s="35" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -9355,7 +9355,7 @@
         </is>
       </c>
       <c r="D50" s="36" t="n">
-        <v>0.1901715392654143</v>
+        <v>0.1901715392654144</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
@@ -9909,7 +9909,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-05</t>
+          <t>UPDATE: 26-10-06</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -10501,7 +10501,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-05</t>
+          <t>UPDATE: 26-10-06</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -24195,7 +24195,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -29200,7 +29200,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -31303,7 +31303,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/059270_model.xlsx
+++ b/argus/kship/models/059270_model.xlsx
@@ -4248,7 +4248,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-06</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-07</t>
         </is>
       </c>
     </row>
@@ -5119,35 +5119,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1351.18</v>
+        <v>1348.08</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1459.61</v>
+        <v>1458.99</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5238,35 +5238,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5357,35 +5357,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>855.39</v>
+        <v>853.26</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>920.6900000000001</v>
+        <v>920.3099999999999</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5476,35 +5476,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5595,35 +5595,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1519.07</v>
+        <v>1516.47</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1693.81</v>
+        <v>1692.86</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5714,35 +5714,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5833,35 +5833,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>201.53</v>
+        <v>201.07</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>214.03</v>
+        <v>213.96</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5952,35 +5952,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6087,7 +6087,7 @@
         <v>5460</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>5480</v>
+        <v>5240</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6269,7 +6269,7 @@
         <v>3980</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>5290</v>
+        <v>5190</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -6360,7 +6360,7 @@
         <v>5525.9</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>5500</v>
+        <v>5440</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -9041,11 +9041,11 @@
         </is>
       </c>
       <c r="D42" s="34" t="n">
-        <v>5480</v>
+        <v>5240</v>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 5,520원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 5,480원)</t>
         </is>
       </c>
       <c r="F42" s="9" t="n"/>
@@ -9081,7 +9081,7 @@
       </c>
       <c r="D43" s="35" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -9909,7 +9909,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-06</t>
+          <t>UPDATE: 26-10-07</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -10501,7 +10501,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-06</t>
+          <t>UPDATE: 26-10-07</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -24195,7 +24195,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -29200,7 +29200,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -31303,7 +31303,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/059270_model.xlsx
+++ b/argus/kship/models/059270_model.xlsx
@@ -4248,7 +4248,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-07</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-08</t>
         </is>
       </c>
     </row>
@@ -9909,7 +9909,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-07</t>
+          <t>UPDATE: 26-10-08</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -10501,7 +10501,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-07</t>
+          <t>UPDATE: 26-10-08</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/059270_model.xlsx
+++ b/argus/kship/models/059270_model.xlsx
@@ -5119,35 +5119,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1348.08</v>
+        <v>1346.2</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1458.99</v>
+        <v>1458.38</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5238,35 +5238,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5357,35 +5357,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>853.26</v>
+        <v>851.8099999999999</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>920.3099999999999</v>
+        <v>919.9299999999999</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5476,35 +5476,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5595,35 +5595,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1516.47</v>
+        <v>1512.43</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1692.86</v>
+        <v>1691.86</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5714,35 +5714,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5833,35 +5833,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>201.07</v>
+        <v>200.79</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.96</v>
+        <v>213.89</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5952,35 +5952,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6087,7 +6087,7 @@
         <v>5460</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>5240</v>
+        <v>5170</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6269,7 +6269,7 @@
         <v>3980</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>5190</v>
+        <v>5050</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -6360,7 +6360,7 @@
         <v>5525.9</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>5440</v>
+        <v>5398</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -9041,7 +9041,7 @@
         </is>
       </c>
       <c r="D42" s="34" t="n">
-        <v>5240</v>
+        <v>5170</v>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
@@ -9081,7 +9081,7 @@
       </c>
       <c r="D43" s="35" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -24195,7 +24195,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -29200,7 +29200,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -31303,7 +31303,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/059270_model.xlsx
+++ b/argus/kship/models/059270_model.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="분기" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="TP" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="외화" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
@@ -1555,79 +1555,19 @@
 유통주식수 유지 — fin.shares.common_outstanding(2026Q2)</t>
       </text>
     </comment>
-    <comment ref="AC38" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 전년동기 − 1
-= EPS(추정 구간은 일회성 미가정)</t>
-      </text>
-    </comment>
     <comment ref="AD38" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 전년동기 − 1
-= EPS(추정 구간은 일회성 미가정)</t>
-      </text>
-    </comment>
-    <comment ref="AF38" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 전년동기 − 1
-= EPS(추정 구간은 일회성 미가정)</t>
-      </text>
-    </comment>
-    <comment ref="AG38" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 전년동기 − 1
-= EPS(추정 구간은 일회성 미가정)</t>
-      </text>
-    </comment>
-    <comment ref="AH38" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 전년동기 − 1
-= EPS(추정 구간은 일회성 미가정)</t>
-      </text>
-    </comment>
-    <comment ref="AI38" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 전년동기 − 1
-= EPS(추정 구간은 일회성 미가정)</t>
-      </text>
-    </comment>
-    <comment ref="AK38" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 전년동기 − 1
-= EPS(추정 구간은 일회성 미가정)</t>
-      </text>
-    </comment>
-    <comment ref="AL38" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 전년동기 − 1
-= EPS(추정 구간은 일회성 미가정)</t>
-      </text>
-    </comment>
-    <comment ref="AM38" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 전년동기 − 1
-= EPS(추정 구간은 일회성 미가정)</t>
-      </text>
-    </comment>
-    <comment ref="AN38" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 전년동기 − 1
-= EPS(추정 구간은 일회성 미가정)</t>
-      </text>
-    </comment>
-    <comment ref="AD39" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
 직전 결산 DPS 0원 유지</t>
       </text>
     </comment>
-    <comment ref="AI39" authorId="0" shapeId="0">
+    <comment ref="AI38" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
 직전 결산 DPS 0원 유지</t>
       </text>
     </comment>
-    <comment ref="AN39" authorId="0" shapeId="0">
+    <comment ref="AN38" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
 직전 결산 DPS 0원 유지</t>
@@ -3288,159 +3228,69 @@
 [per_share]</t>
       </text>
     </comment>
-    <comment ref="E31" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
-      </text>
-    </comment>
-    <comment ref="G31" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
-      </text>
-    </comment>
-    <comment ref="H31" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
-      </text>
-    </comment>
-    <comment ref="I31" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
-      </text>
-    </comment>
-    <comment ref="J31" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
-      </text>
-    </comment>
-    <comment ref="L31" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
-      </text>
-    </comment>
-    <comment ref="M31" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
-      </text>
-    </comment>
-    <comment ref="N31" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
-      </text>
-    </comment>
-    <comment ref="O31" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
-      </text>
-    </comment>
-    <comment ref="Q31" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
-      </text>
-    </comment>
-    <comment ref="R31" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
-      </text>
-    </comment>
-    <comment ref="S31" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
-      </text>
-    </comment>
-    <comment ref="T31" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
-      </text>
-    </comment>
-    <comment ref="V31" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
-      </text>
-    </comment>
-    <comment ref="W31" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
-      </text>
-    </comment>
-    <comment ref="X31" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
-      </text>
-    </comment>
-    <comment ref="Y31" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
-      </text>
-    </comment>
-    <comment ref="AA31" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
-      </text>
-    </comment>
     <comment ref="AB31" authorId="0" shapeId="0">
       <text>
-        <t>추정(실적 구간 갭필): 지배NI 13억 − (비영업손익 20억 − 12분기 기준선 0억) × (1 − 0.0%, 분기 유효세율(법인세 0억 ÷ 세전 13억)) × 지배 비중 1.00(그 분기 지배NI/NI) = -7억 ÷ 유통주식수 — 일회성 여부·세효과는 주석 미확인(모델 추정); 보고 EPS 114.5원</t>
+        <t>조정EPS 산식(모델 추정, 일회성 여부·세효과 주석 미확인): 지배NI − 초과 비영업손익 20억 × (1 − 세율 0.0% [분기 유효세율(법인세 0억 ÷ 세전 13억)]) × 지배 비중 1.0000 [그 분기 지배NI/NI] = -7억 ÷ 유통주식수 · 초과 = 비영업손익 20억 − 12분기 기준선 0억 · 보고 EPS 114원(EPS 행 불변) · 상수 19.83·1.0 는 모델 one_offs_detected 값(세전·법인세 셀을 바꿔도 재계산되지 않음)</t>
       </text>
     </comment>
     <comment ref="AC31" authorId="0" shapeId="0">
       <text>
         <t>추정: = EPS(추정 구간은 일회성 미가정)
-[yoy]</t>
+[identity]</t>
       </text>
     </comment>
     <comment ref="AD31" authorId="0" shapeId="0">
       <text>
         <t>추정: = EPS(추정 구간은 일회성 미가정)
-[yoy]</t>
+[identity]</t>
       </text>
     </comment>
     <comment ref="AF31" authorId="0" shapeId="0">
       <text>
         <t>추정: = EPS(추정 구간은 일회성 미가정)
-[yoy]</t>
+[identity]</t>
       </text>
     </comment>
     <comment ref="AG31" authorId="0" shapeId="0">
       <text>
         <t>추정: = EPS(추정 구간은 일회성 미가정)
-[yoy]</t>
+[identity]</t>
       </text>
     </comment>
     <comment ref="AH31" authorId="0" shapeId="0">
       <text>
         <t>추정: = EPS(추정 구간은 일회성 미가정)
-[yoy]</t>
+[identity]</t>
       </text>
     </comment>
     <comment ref="AI31" authorId="0" shapeId="0">
       <text>
         <t>추정: = EPS(추정 구간은 일회성 미가정)
-[yoy]</t>
+[identity]</t>
       </text>
     </comment>
     <comment ref="AK31" authorId="0" shapeId="0">
       <text>
         <t>추정: = EPS(추정 구간은 일회성 미가정)
-[yoy]</t>
+[identity]</t>
       </text>
     </comment>
     <comment ref="AL31" authorId="0" shapeId="0">
       <text>
         <t>추정: = EPS(추정 구간은 일회성 미가정)
-[yoy]</t>
+[identity]</t>
       </text>
     </comment>
     <comment ref="AM31" authorId="0" shapeId="0">
       <text>
         <t>추정: = EPS(추정 구간은 일회성 미가정)
-[yoy]</t>
+[identity]</t>
       </text>
     </comment>
     <comment ref="AN31" authorId="0" shapeId="0">
       <text>
         <t>추정: = EPS(추정 구간은 일회성 미가정)
-[yoy]</t>
+[identity]</t>
       </text>
     </comment>
     <comment ref="AC32" authorId="0" shapeId="0">
@@ -4232,7 +4082,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A34"/>
+  <dimension ref="A1:A35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="160" customWidth="1" min="1" max="1"/>
@@ -4248,7 +4098,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-08</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-09</t>
         </is>
       </c>
     </row>
@@ -4286,7 +4136,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>subQ      분기 서브모델(억원 = 백만원/100). 확정 행: =IFERROR(VLOOKUP($D행,BS연결,MATCH(E$1,BS연결H,0),0)/100,"")  추정 행: 변수 시트 가정 셀 참조 수식. 외환손익·파생상품손익은 BS 계정 합·차, 기타금융손익은 잔차, OPM·EPS·BPS·PER·PBR 은 파생 수식</t>
+          <t>subQ      분기 서브모델(억원 = 백만원/100). 확정 행: =IFERROR(VLOOKUP($D행,BS연결,MATCH(E$1,BS연결H,0),0)/100,"")  추정 행: 변수 시트 가정 셀 참조 수식. 외환손익·파생상품손익은 BS 계정 합·차, 기타금융손익은 잔차, OPM·EPS·BPS·PER·PBR 은 파생 수식, 조정EPS 는 EPS 참조(일회성 의심 분기만 산식 셀)</t>
         </is>
       </c>
     </row>
@@ -4411,50 +4261,57 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>· 연결된 가정: 판관비율, 지배주주비중, 이자율 · 연결 안 된 가정(모델값·분기별 역산 그대로): 세율(MAX(세전,0)×단일 세율로 재현 불가(지주 자회사 합산 등) → 분기별 역산)</t>
+          <t>· 조정EPS(일회성 의심 1분기: 2026Q2 보고 114→조정 -63원) — 의심 분기 = 지배NI − (비영업손익 − 12분기 기준선) × (1 − 세율) × 지배 비중 ÷ 유통주식수(subQ 수식+메모, 세후 초과·지배 비중은 모델 상수), 다른 분기 = EPS. 보고 EPS 행·TP 12M fwd EPS(추정 분기만) 는 불변. 일회성 여부·세효과는 주석 미확인(모델 추정)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>· 연결된 가정: 판관비율, 지배주주비중, 이자율 · 연결 안 된 가정(모델값·분기별 역산 그대로): 세율(MAX(세전,0)×단일 세율로 재현 불가(지주 자회사 합산 등) → 분기별 역산)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>· 밸류에이션 — PER 밴드 10.0/15.0/20.0배(sector_default(레퍼런스 TP_PE PB 예시 10/15/20배; 과거 PER 중위 639.1배가 3~40 밖(턴어라운드 왜곡))) · COE 9.0% · 12M fwd EPS 가중 0.5(가정). 모델 산출값 구간이며 추천이 아니다</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="inlineStr"/>
-    </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>출처: DART 정기보고서(연결/별도 재무제표·주석), FnGuide 계정명 규약, ECB 환율(api.frankfurter.app), 종가 네이버 정규장(aikstockdata 금융위 확정종가 대조·출처표기·비영리), 척당 계약 공시(contracts.json), forecast_panel(신규수주 패널)</t>
-        </is>
-      </c>
+      <c r="A30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>재현: cd argus/kship/tools &amp;&amp; python3 kship_model_xlsx.py --model assets/models/059270.json --verify   (모델 json 부터: kship_model.py --build --all --xlsx · xlsx 58사 일괄: kship_model_xlsx.py --all --verify)</t>
+          <t>출처: DART 정기보고서(연결/별도 재무제표·주석), FnGuide 계정명 규약, ECB 환율(api.frankfurter.app), 종가 네이버 정규장(aikstockdata 금융위 확정종가 대조·출처표기·비영리), 척당 계약 공시(contracts.json), forecast_panel(신규수주 패널)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>검증(--verify): 추정 전 분기·실적 수식 셀을 자체 계산기로 재계산해 모델값과 대조(억원 ±0.05), 세율·OPM·환율 forward·이자율·신규수주 셀을 바꿔 종속 셀이 기대만큼 움직이는지 확인. Excel 실개봉은 미확인(LibreOffice/Excel 없음)</t>
+          <t>재현: cd argus/kship/tools &amp;&amp; python3 kship_model_xlsx.py --model assets/models/059270.json --verify   (모델 json 부터: kship_model.py --build --all --xlsx · xlsx 58사 일괄: kship_model_xlsx.py --all --verify)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>한계: 모델 quality.warnings — 매출 드라이버 폴백(고객 연동 OOS 기각 — 동결 2025Q2 이후 4분기 매출 WAPE 연동 30.3% &gt; 추세 14.0% × 1.10 (suppliers_mentions·시차 2·4분기 이동합·창 19, r=0.77 유의)): 전년동기 × (1+g) 추세 / 감가상각비가 face·CF 에 없음(주석 미파싱) → EBITDA·EV/EBITDA 미산출 / 일회성 의심 2026Q2: 비영업손익 20억(영업이익 -7억의 3배, 12분기 중위 0억·기준선 0억) → 지배NI 13억·보고 EPS·FY2026 합계·TTM PER 에 그대로 포함 — 처분이익 등 일회성 여부는 주석 확인 전까지 미확정(12M fwd EPS 에는 미포함) · 조정EPS -63.1원(보고 114.5원; 초과 비영업손익 20억 × (1 − 세율 0.0%) × 지배 비중 1.00 = 20억 차감 — 추정, 조정EPS 행) / 금융손익 실적→추정 단절: 최근 4분기 실적 -0/-0/-0/+20(중위 -0억) → 추정 2026Q3 +1억(차 +1억, +937%) — 추정은 이자손익 + 기타금융 중위, 외환·파생 평가손익 0 가정(환율 효과는 환관련손익 행). 값은 바꾸지 않음 — 지배NI·EPS 해석 시 참고</t>
+          <t>검증(--verify): 추정 전 분기·실적 수식 셀을 자체 계산기로 재계산해 모델값과 대조(억원 ±0.05), 세율·OPM·환율 forward·이자율·신규수주 셀을 바꿔 종속 셀이 기대만큼 움직이는지 확인. Excel 실개봉은 미확인(LibreOffice/Excel 없음)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
+        <is>
+          <t>한계: 모델 quality.warnings — 매출 드라이버 폴백(고객 연동 OOS 기각 — 동결 2025Q2 이후 4분기 매출 WAPE 연동 30.3% &gt; 추세 14.0% × 1.10 (suppliers_mentions·시차 2·4분기 이동합·창 19, r=0.77 유의)): 전년동기 × (1+g) 추세 / 감가상각비가 face·CF 에 없음(주석 미파싱) → EBITDA·EV/EBITDA 미산출 / 일회성 의심 2026Q2: 비영업손익 20억(영업이익 -7억의 3배, 12분기 중위 0억·기준선 0억) → 지배NI 13억·보고 EPS·FY2026 합계·TTM PER 에 그대로 포함 — 처분이익 등 일회성 여부는 주석 확인 전까지 미확정(12M fwd EPS 에는 미포함) · 조정EPS -63.1원(보고 114.5원; 초과 비영업손익 20억 × (1 − 세율 0.0%) × 지배 비중 1.00 = 20억 차감 — 추정, 조정EPS 행) / 금융손익 실적→추정 단절: 최근 4분기 실적 -0/-0/-0/+20(중위 -0억) → 추정 2026Q3 +1억(차 +1억, +937%) — 추정은 이자손익 + 기타금융 중위, 외환·파생 평가손익 0 가정(환율 효과는 환관련손익 행). 값은 바꾸지 않음 — 지배NI·EPS 해석 시 참고</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
         <is>
           <t>백테스트: {"freeze": "2025Q2", "horizon": 4, "revenue_wape_pct": 14.0, "op_wape_pct": 60.1, "n": 4, "note": "단일 회사 4분기 — 통계 아님", "driver_at_freeze": "trend_seasonal", "selection_oos_at_freeze": {"wape_link": null, "wape_trend": null, "adopted": false, "decision": "rejected", "note": "유의성 조건 미달 → OOS 비교 전 기각"}, "frozen_inputs": "fin(연결/별도)·고객 조선사 모델·지주 자회사 모델은 2025Q2 까지의 분기만; 선표는 체결일 ≤ 2025Q2 말일 계약(원장 최신 금액·코호트 등급, 환산 없음); 잔고는 yards_cache 2025Q2; 시세·환율 forward·prices·forecast_panel 신규수주 미사용. 고객 가중치(suppliers.json 언급 비중)와 합병 체인링크는 현재 지식; 고객 연동 채택은 동결 모델 안에서도 자기 la−4분기 OOS 규칙(selection_oos_at_freeze)", "detail": [{"q": "2025Q3", "rev_pred": 33.32, "rev_act": 38.02, "op_pred": -2.52, "op_act": -0.27}, {"q": "2025Q4", "rev_pred": 35.25, "rev_act": 42.11, "op_pred": -2.67, "op_act": -2.29}, {"q": "2026Q1", "rev_pred": 30.03, "rev_act": 32.86, "op_pred": -2.27, "op_act": -3.04}, {"q": "2026Q2", "rev_pred": 39.2, "rev_act": 33.15, "op_pred": -2.97, "op_act": -7.36}]}</t>
         </is>
@@ -4471,7 +4328,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO57"/>
+  <dimension ref="A1:AO56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -6658,11 +6515,11 @@
         <v/>
       </c>
       <c r="AC22" s="26">
-        <f>$D$50</f>
+        <f>$D$49</f>
         <v/>
       </c>
       <c r="AD22" s="26">
-        <f>$D$50</f>
+        <f>$D$49</f>
         <v/>
       </c>
       <c r="AE22" s="25">
@@ -6670,19 +6527,19 @@
         <v/>
       </c>
       <c r="AF22" s="26">
-        <f>$D$50</f>
+        <f>$D$49</f>
         <v/>
       </c>
       <c r="AG22" s="26">
-        <f>$D$50</f>
+        <f>$D$49</f>
         <v/>
       </c>
       <c r="AH22" s="26">
-        <f>$D$50</f>
+        <f>$D$49</f>
         <v/>
       </c>
       <c r="AI22" s="26">
-        <f>$D$50</f>
+        <f>$D$49</f>
         <v/>
       </c>
       <c r="AJ22" s="25">
@@ -6690,19 +6547,19 @@
         <v/>
       </c>
       <c r="AK22" s="26">
-        <f>$D$50</f>
+        <f>$D$49</f>
         <v/>
       </c>
       <c r="AL22" s="26">
-        <f>$D$50</f>
+        <f>$D$49</f>
         <v/>
       </c>
       <c r="AM22" s="26">
-        <f>$D$50</f>
+        <f>$D$49</f>
         <v/>
       </c>
       <c r="AN22" s="26">
-        <f>$D$50</f>
+        <f>$D$49</f>
         <v/>
       </c>
       <c r="AO22" s="25">
@@ -7443,11 +7300,11 @@
         <v/>
       </c>
       <c r="AC27" s="26">
-        <f>$D$51</f>
+        <f>$D$50</f>
         <v/>
       </c>
       <c r="AD27" s="26">
-        <f>$D$51</f>
+        <f>$D$50</f>
         <v/>
       </c>
       <c r="AE27" s="25">
@@ -7455,19 +7312,19 @@
         <v/>
       </c>
       <c r="AF27" s="26">
-        <f>$D$51</f>
+        <f>$D$50</f>
         <v/>
       </c>
       <c r="AG27" s="26">
-        <f>$D$51</f>
+        <f>$D$50</f>
         <v/>
       </c>
       <c r="AH27" s="26">
-        <f>$D$51</f>
+        <f>$D$50</f>
         <v/>
       </c>
       <c r="AI27" s="26">
-        <f>$D$51</f>
+        <f>$D$50</f>
         <v/>
       </c>
       <c r="AJ27" s="25">
@@ -7475,19 +7332,19 @@
         <v/>
       </c>
       <c r="AK27" s="26">
-        <f>$D$51</f>
+        <f>$D$50</f>
         <v/>
       </c>
       <c r="AL27" s="26">
-        <f>$D$51</f>
+        <f>$D$50</f>
         <v/>
       </c>
       <c r="AM27" s="26">
-        <f>$D$51</f>
+        <f>$D$50</f>
         <v/>
       </c>
       <c r="AN27" s="26">
-        <f>$D$51</f>
+        <f>$D$50</f>
         <v/>
       </c>
       <c r="AO27" s="25">
@@ -8720,264 +8577,176 @@
     <row r="38">
       <c r="A38" s="12" t="inlineStr">
         <is>
-          <t>drv:조정EPS</t>
+          <t>drv:DPS</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>yoy</t>
+          <t>abs</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>조정EPS YoY</t>
-        </is>
-      </c>
-      <c r="E38" s="21" t="n"/>
-      <c r="F38" s="22" t="n"/>
-      <c r="G38" s="21" t="n"/>
-      <c r="H38" s="21" t="n"/>
-      <c r="I38" s="21" t="n"/>
-      <c r="J38" s="21">
-        <f>IFERROR(subQ!J31/subQ!E31-1,"")</f>
-        <v/>
-      </c>
-      <c r="K38" s="22" t="n"/>
-      <c r="L38" s="21">
-        <f>IFERROR(subQ!L31/subQ!G31-1,"")</f>
-        <v/>
-      </c>
-      <c r="M38" s="21">
-        <f>IFERROR(subQ!M31/subQ!H31-1,"")</f>
-        <v/>
-      </c>
-      <c r="N38" s="21">
-        <f>IFERROR(subQ!N31/subQ!I31-1,"")</f>
-        <v/>
-      </c>
-      <c r="O38" s="21">
-        <f>IFERROR(subQ!O31/subQ!J31-1,"")</f>
-        <v/>
-      </c>
-      <c r="P38" s="22" t="n"/>
-      <c r="Q38" s="21">
-        <f>IFERROR(subQ!Q31/subQ!L31-1,"")</f>
-        <v/>
-      </c>
-      <c r="R38" s="21">
-        <f>IFERROR(subQ!R31/subQ!M31-1,"")</f>
-        <v/>
-      </c>
-      <c r="S38" s="21">
-        <f>IFERROR(subQ!S31/subQ!N31-1,"")</f>
-        <v/>
-      </c>
-      <c r="T38" s="21">
-        <f>IFERROR(subQ!T31/subQ!O31-1,"")</f>
-        <v/>
-      </c>
-      <c r="U38" s="22" t="n"/>
-      <c r="V38" s="21">
-        <f>IFERROR(subQ!V31/subQ!Q31-1,"")</f>
-        <v/>
-      </c>
-      <c r="W38" s="21">
-        <f>IFERROR(subQ!W31/subQ!R31-1,"")</f>
-        <v/>
-      </c>
-      <c r="X38" s="21">
-        <f>IFERROR(subQ!X31/subQ!S31-1,"")</f>
-        <v/>
-      </c>
-      <c r="Y38" s="21">
-        <f>IFERROR(subQ!Y31/subQ!T31-1,"")</f>
-        <v/>
-      </c>
-      <c r="Z38" s="22" t="n"/>
-      <c r="AA38" s="21">
-        <f>IFERROR(subQ!AA31/subQ!V31-1,"")</f>
-        <v/>
-      </c>
-      <c r="AB38" s="23">
-        <f>IFERROR(subQ!AB31/subQ!W31-1,"")</f>
-        <v/>
-      </c>
-      <c r="AC38" s="24" t="n">
-        <v>1.714285714</v>
-      </c>
-      <c r="AD38" s="24" t="n">
-        <v>-0.495726496</v>
-      </c>
-      <c r="AE38" s="25" t="n"/>
-      <c r="AF38" s="24" t="n">
-        <v>-0.724</v>
-      </c>
-      <c r="AG38" s="24" t="n">
-        <v>-0.88748019</v>
-      </c>
-      <c r="AH38" s="24" t="n">
-        <v>0.06315789500000001</v>
-      </c>
-      <c r="AI38" s="24" t="n">
-        <v>0.050847458</v>
-      </c>
-      <c r="AJ38" s="25" t="n"/>
-      <c r="AK38" s="24" t="n">
-        <v>0.072463768</v>
-      </c>
-      <c r="AL38" s="24" t="n">
-        <v>0.07042253499999999</v>
-      </c>
-      <c r="AM38" s="24" t="n">
-        <v>0.03960396</v>
-      </c>
-      <c r="AN38" s="24" t="n">
-        <v>0.032258065</v>
-      </c>
-      <c r="AO38" s="25" t="n"/>
+          <t>DPS (가정, 원)</t>
+        </is>
+      </c>
+      <c r="E38" s="27">
+        <f>subQ!E33</f>
+        <v/>
+      </c>
+      <c r="F38" s="28">
+        <f>subQ!F33</f>
+        <v/>
+      </c>
+      <c r="G38" s="27">
+        <f>subQ!G33</f>
+        <v/>
+      </c>
+      <c r="H38" s="27">
+        <f>subQ!H33</f>
+        <v/>
+      </c>
+      <c r="I38" s="27">
+        <f>subQ!I33</f>
+        <v/>
+      </c>
+      <c r="J38" s="27">
+        <f>subQ!J33</f>
+        <v/>
+      </c>
+      <c r="K38" s="28">
+        <f>subQ!K33</f>
+        <v/>
+      </c>
+      <c r="L38" s="27">
+        <f>subQ!L33</f>
+        <v/>
+      </c>
+      <c r="M38" s="27">
+        <f>subQ!M33</f>
+        <v/>
+      </c>
+      <c r="N38" s="27">
+        <f>subQ!N33</f>
+        <v/>
+      </c>
+      <c r="O38" s="27">
+        <f>subQ!O33</f>
+        <v/>
+      </c>
+      <c r="P38" s="28">
+        <f>subQ!P33</f>
+        <v/>
+      </c>
+      <c r="Q38" s="27">
+        <f>subQ!Q33</f>
+        <v/>
+      </c>
+      <c r="R38" s="27">
+        <f>subQ!R33</f>
+        <v/>
+      </c>
+      <c r="S38" s="27">
+        <f>subQ!S33</f>
+        <v/>
+      </c>
+      <c r="T38" s="27">
+        <f>subQ!T33</f>
+        <v/>
+      </c>
+      <c r="U38" s="28">
+        <f>subQ!U33</f>
+        <v/>
+      </c>
+      <c r="V38" s="27">
+        <f>subQ!V33</f>
+        <v/>
+      </c>
+      <c r="W38" s="27">
+        <f>subQ!W33</f>
+        <v/>
+      </c>
+      <c r="X38" s="27">
+        <f>subQ!X33</f>
+        <v/>
+      </c>
+      <c r="Y38" s="27">
+        <f>subQ!Y33</f>
+        <v/>
+      </c>
+      <c r="Z38" s="28">
+        <f>subQ!Z33</f>
+        <v/>
+      </c>
+      <c r="AA38" s="27">
+        <f>subQ!AA33</f>
+        <v/>
+      </c>
+      <c r="AB38" s="29">
+        <f>subQ!AB33</f>
+        <v/>
+      </c>
+      <c r="AC38" s="33" t="n"/>
+      <c r="AD38" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE38" s="31">
+        <f>subQ!AE33</f>
+        <v/>
+      </c>
+      <c r="AF38" s="33" t="n"/>
+      <c r="AG38" s="33" t="n"/>
+      <c r="AH38" s="33" t="n"/>
+      <c r="AI38" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ38" s="31">
+        <f>subQ!AJ33</f>
+        <v/>
+      </c>
+      <c r="AK38" s="33" t="n"/>
+      <c r="AL38" s="33" t="n"/>
+      <c r="AM38" s="33" t="n"/>
+      <c r="AN38" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO38" s="31">
+        <f>subQ!AO33</f>
+        <v/>
+      </c>
     </row>
     <row r="39">
-      <c r="A39" s="12" t="inlineStr">
-        <is>
-          <t>drv:DPS</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>abs</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>DPS (가정, 원)</t>
-        </is>
-      </c>
-      <c r="E39" s="27">
-        <f>subQ!E33</f>
-        <v/>
-      </c>
-      <c r="F39" s="28">
-        <f>subQ!F33</f>
-        <v/>
-      </c>
-      <c r="G39" s="27">
-        <f>subQ!G33</f>
-        <v/>
-      </c>
-      <c r="H39" s="27">
-        <f>subQ!H33</f>
-        <v/>
-      </c>
-      <c r="I39" s="27">
-        <f>subQ!I33</f>
-        <v/>
-      </c>
-      <c r="J39" s="27">
-        <f>subQ!J33</f>
-        <v/>
-      </c>
-      <c r="K39" s="28">
-        <f>subQ!K33</f>
-        <v/>
-      </c>
-      <c r="L39" s="27">
-        <f>subQ!L33</f>
-        <v/>
-      </c>
-      <c r="M39" s="27">
-        <f>subQ!M33</f>
-        <v/>
-      </c>
-      <c r="N39" s="27">
-        <f>subQ!N33</f>
-        <v/>
-      </c>
-      <c r="O39" s="27">
-        <f>subQ!O33</f>
-        <v/>
-      </c>
-      <c r="P39" s="28">
-        <f>subQ!P33</f>
-        <v/>
-      </c>
-      <c r="Q39" s="27">
-        <f>subQ!Q33</f>
-        <v/>
-      </c>
-      <c r="R39" s="27">
-        <f>subQ!R33</f>
-        <v/>
-      </c>
-      <c r="S39" s="27">
-        <f>subQ!S33</f>
-        <v/>
-      </c>
-      <c r="T39" s="27">
-        <f>subQ!T33</f>
-        <v/>
-      </c>
-      <c r="U39" s="28">
-        <f>subQ!U33</f>
-        <v/>
-      </c>
-      <c r="V39" s="27">
-        <f>subQ!V33</f>
-        <v/>
-      </c>
-      <c r="W39" s="27">
-        <f>subQ!W33</f>
-        <v/>
-      </c>
-      <c r="X39" s="27">
-        <f>subQ!X33</f>
-        <v/>
-      </c>
-      <c r="Y39" s="27">
-        <f>subQ!Y33</f>
-        <v/>
-      </c>
-      <c r="Z39" s="28">
-        <f>subQ!Z33</f>
-        <v/>
-      </c>
-      <c r="AA39" s="27">
-        <f>subQ!AA33</f>
-        <v/>
-      </c>
-      <c r="AB39" s="29">
-        <f>subQ!AB33</f>
-        <v/>
-      </c>
-      <c r="AC39" s="33" t="n"/>
-      <c r="AD39" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE39" s="31">
-        <f>subQ!AE33</f>
-        <v/>
-      </c>
-      <c r="AF39" s="33" t="n"/>
-      <c r="AG39" s="33" t="n"/>
-      <c r="AH39" s="33" t="n"/>
-      <c r="AI39" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ39" s="31">
-        <f>subQ!AJ33</f>
-        <v/>
-      </c>
-      <c r="AK39" s="33" t="n"/>
-      <c r="AL39" s="33" t="n"/>
-      <c r="AM39" s="33" t="n"/>
-      <c r="AN39" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO39" s="31">
-        <f>subQ!AO33</f>
-        <v/>
-      </c>
+      <c r="F39" s="9" t="n"/>
+      <c r="K39" s="9" t="n"/>
+      <c r="P39" s="9" t="n"/>
+      <c r="U39" s="9" t="n"/>
+      <c r="Z39" s="9" t="n"/>
+      <c r="AB39" s="5" t="n"/>
+      <c r="AC39" s="10" t="n"/>
+      <c r="AD39" s="10" t="n"/>
+      <c r="AE39" s="11" t="n"/>
+      <c r="AF39" s="10" t="n"/>
+      <c r="AG39" s="10" t="n"/>
+      <c r="AH39" s="10" t="n"/>
+      <c r="AI39" s="10" t="n"/>
+      <c r="AJ39" s="11" t="n"/>
+      <c r="AK39" s="10" t="n"/>
+      <c r="AL39" s="10" t="n"/>
+      <c r="AM39" s="10" t="n"/>
+      <c r="AN39" s="10" t="n"/>
+      <c r="AO39" s="11" t="n"/>
     </row>
     <row r="40">
+      <c r="B40" s="1" t="inlineStr">
+        <is>
+          <t>3. 밸류에이션·스칼라</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>노란 셀 = 가정. '연결' 표시는 추정 전 분기 수식이 이 셀을 참조한다는 뜻</t>
+        </is>
+      </c>
       <c r="F40" s="9" t="n"/>
       <c r="K40" s="9" t="n"/>
       <c r="P40" s="9" t="n"/>
@@ -8999,14 +8768,22 @@
       <c r="AO40" s="11" t="n"/>
     </row>
     <row r="41">
-      <c r="B41" s="1" t="inlineStr">
-        <is>
-          <t>3. 밸류에이션·스칼라</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>노란 셀 = 가정. '연결' 표시는 추정 전 분기 수식이 이 셀을 참조한다는 뜻</t>
+      <c r="A41" s="12" t="inlineStr">
+        <is>
+          <t>sc:종가</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>종가</t>
+        </is>
+      </c>
+      <c r="D41" s="34" t="n">
+        <v>5170</v>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 5,480원)</t>
         </is>
       </c>
       <c r="F41" s="9" t="n"/>
@@ -9032,20 +8809,22 @@
     <row r="42">
       <c r="A42" s="12" t="inlineStr">
         <is>
-          <t>sc:종가</t>
+          <t>sc:기준일</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>종가</t>
-        </is>
-      </c>
-      <c r="D42" s="34" t="n">
-        <v>5170</v>
+          <t>기준일</t>
+        </is>
+      </c>
+      <c r="D42" s="35" t="inlineStr">
+        <is>
+          <t>20261008</t>
+        </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 5,480원)</t>
+          <t>종가 기준일</t>
         </is>
       </c>
       <c r="F42" s="9" t="n"/>
@@ -9071,22 +8850,20 @@
     <row r="43">
       <c r="A43" s="12" t="inlineStr">
         <is>
-          <t>sc:기준일</t>
+          <t>sc:COE</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>기준일</t>
-        </is>
-      </c>
-      <c r="D43" s="35" t="inlineStr">
-        <is>
-          <t>20261008</t>
-        </is>
+          <t>COE</t>
+        </is>
+      </c>
+      <c r="D43" s="24" t="n">
+        <v>0.09</v>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>종가 기준일</t>
+          <t>자기자본비용(가정) — TP 적정 PBR = ROE/COE</t>
         </is>
       </c>
       <c r="F43" s="9" t="n"/>
@@ -9112,20 +8889,20 @@
     <row r="44">
       <c r="A44" s="12" t="inlineStr">
         <is>
-          <t>sc:COE</t>
+          <t>sc:PER_lo</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>COE</t>
-        </is>
-      </c>
-      <c r="D44" s="24" t="n">
-        <v>0.09</v>
+          <t>PER_lo</t>
+        </is>
+      </c>
+      <c r="D44" s="30" t="n">
+        <v>10</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>자기자본비용(가정) — TP 적정 PBR = ROE/COE</t>
+          <t>PER 밴드 하단(배) — sector_default(레퍼런스 TP_PE PB 예시 10/15/20배; 과거 PER 중위 639.1배가 3~40 밖(턴어라운드 왜곡))</t>
         </is>
       </c>
       <c r="F44" s="9" t="n"/>
@@ -9151,20 +8928,20 @@
     <row r="45">
       <c r="A45" s="12" t="inlineStr">
         <is>
-          <t>sc:PER_lo</t>
+          <t>sc:PER_mid</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>PER_lo</t>
+          <t>PER_mid</t>
         </is>
       </c>
       <c r="D45" s="30" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>PER 밴드 하단(배) — sector_default(레퍼런스 TP_PE PB 예시 10/15/20배; 과거 PER 중위 639.1배가 3~40 밖(턴어라운드 왜곡))</t>
+          <t>PER 밴드 중단(배)</t>
         </is>
       </c>
       <c r="F45" s="9" t="n"/>
@@ -9190,20 +8967,20 @@
     <row r="46">
       <c r="A46" s="12" t="inlineStr">
         <is>
-          <t>sc:PER_mid</t>
+          <t>sc:PER_hi</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>PER_mid</t>
+          <t>PER_hi</t>
         </is>
       </c>
       <c r="D46" s="30" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>PER 밴드 중단(배)</t>
+          <t>PER 밴드 상단(배)</t>
         </is>
       </c>
       <c r="F46" s="9" t="n"/>
@@ -9229,20 +9006,20 @@
     <row r="47">
       <c r="A47" s="12" t="inlineStr">
         <is>
-          <t>sc:PER_hi</t>
+          <t>sc:EPS_Y1가중</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>PER_hi</t>
-        </is>
-      </c>
-      <c r="D47" s="30" t="n">
-        <v>20</v>
+          <t>EPS_Y1가중</t>
+        </is>
+      </c>
+      <c r="D47" s="24" t="n">
+        <v>0.5</v>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>PER 밴드 상단(배)</t>
+          <t>12M fwd EPS = FY(last_actual연도)E × w + FY+1E × (1−w) — 기준 분기 2Q 이면 0.5(가정)</t>
         </is>
       </c>
       <c r="F47" s="9" t="n"/>
@@ -9268,20 +9045,20 @@
     <row r="48">
       <c r="A48" s="12" t="inlineStr">
         <is>
-          <t>sc:EPS_Y1가중</t>
+          <t>sc:세율</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>EPS_Y1가중</t>
-        </is>
-      </c>
-      <c r="D48" s="24" t="n">
-        <v>0.5</v>
+          <t>세율</t>
+        </is>
+      </c>
+      <c r="D48" s="36" t="n">
+        <v>0.22</v>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>12M fwd EPS = FY(last_actual연도)E × w + FY+1E × (1−w) — 기준 분기 2Q 이면 0.5(가정)</t>
+          <t>참고(연결 안 됨: MAX(세전,0)×단일 세율로 재현 불가(지주 자회사 합산 등) → 분기별 역산) — 모델 assumptions 값 · 최근 12분기 세전 합 ≤ 0; 세전 &gt; 0 분기 중위 0.0% 도 5~27% 밖 → 법정세율 근사 22% 가정</t>
         </is>
       </c>
       <c r="F48" s="9" t="n"/>
@@ -9307,20 +9084,20 @@
     <row r="49">
       <c r="A49" s="12" t="inlineStr">
         <is>
-          <t>sc:세율</t>
+          <t>sc:판관비율</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>세율</t>
+          <t>판관비율</t>
         </is>
       </c>
       <c r="D49" s="36" t="n">
-        <v>0.22</v>
+        <v>0.1901715392654143</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>참고(연결 안 됨: MAX(세전,0)×단일 세율로 재현 불가(지주 자회사 합산 등) → 분기별 역산) — 모델 assumptions 값 · 최근 12분기 세전 합 ≤ 0; 세전 &gt; 0 분기 중위 0.0% 도 5~27% 밖 → 법정세율 근사 22% 가정</t>
+          <t>연결 — 판관비 = 매출액 × 판관비율(역산, 재현 오차 ≤ 0.05억 · 모델 assumptions 0.1902)</t>
         </is>
       </c>
       <c r="F49" s="9" t="n"/>
@@ -9346,20 +9123,20 @@
     <row r="50">
       <c r="A50" s="12" t="inlineStr">
         <is>
-          <t>sc:판관비율</t>
+          <t>sc:지배주주비중</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>판관비율</t>
+          <t>지배주주비중</t>
         </is>
       </c>
       <c r="D50" s="36" t="n">
-        <v>0.1901715392654144</v>
+        <v>1</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>연결 — 판관비 = 매출액 × 판관비율(역산, 재현 오차 ≤ 0.05억 · 모델 assumptions 0.1902)</t>
+          <t>연결 — 지배주주순이익 = 당기순이익 × 비중(역산, 재현 오차 ≤ 0.05억)</t>
         </is>
       </c>
       <c r="F50" s="9" t="n"/>
@@ -9385,20 +9162,20 @@
     <row r="51">
       <c r="A51" s="12" t="inlineStr">
         <is>
-          <t>sc:지배주주비중</t>
+          <t>sc:이자율_자산</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>지배주주비중</t>
+          <t>이자율_자산</t>
         </is>
       </c>
       <c r="D51" s="36" t="n">
-        <v>1</v>
+        <v>0.0217382951702637</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>연결 — 지배주주순이익 = 당기순이익 × 비중(역산, 재현 오차 ≤ 0.05억)</t>
+          <t>연결 — 이자손익 = (전분기 이자발생자산 × 자산이자율 − 전분기 총차입금 × 부채이자율)/4(역산, 재현 오차 ≤ 0.05억 · 모델 assumptions 0.0203)</t>
         </is>
       </c>
       <c r="F51" s="9" t="n"/>
@@ -9424,20 +9201,20 @@
     <row r="52">
       <c r="A52" s="12" t="inlineStr">
         <is>
-          <t>sc:이자율_자산</t>
+          <t>sc:이자율_부채</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>이자율_자산</t>
+          <t>이자율_부채</t>
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.0217382951702637</v>
+        <v>0.001467345107112027</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>연결 — 이자손익 = (전분기 이자발생자산 × 자산이자율 − 전분기 총차입금 × 부채이자율)/4(역산, 재현 오차 ≤ 0.05억 · 모델 assumptions 0.0203)</t>
+          <t>연결 — 같은 수식의 부채 쪽(총차입금 행이 없으면 0)(역산, 재현 오차 ≤ 0.05억)</t>
         </is>
       </c>
       <c r="F52" s="9" t="n"/>
@@ -9463,20 +9240,20 @@
     <row r="53">
       <c r="A53" s="12" t="inlineStr">
         <is>
-          <t>sc:이자율_부채</t>
+          <t>sc:배당성향</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>이자율_부채</t>
-        </is>
-      </c>
-      <c r="D53" s="36" t="n">
-        <v>0.001467345107112027</v>
+          <t>배당성향</t>
+        </is>
+      </c>
+      <c r="D53" s="24" t="n">
+        <v>0</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>연결 — 같은 수식의 부채 쪽(총차입금 행이 없으면 0)(역산, 재현 오차 ≤ 0.05억)</t>
+          <t>배당성향(참고 — 모델은 직전 DPS 유지·Q2 지급 가정)</t>
         </is>
       </c>
       <c r="F53" s="9" t="n"/>
@@ -9502,20 +9279,18 @@
     <row r="54">
       <c r="A54" s="12" t="inlineStr">
         <is>
-          <t>sc:배당성향</t>
+          <t>sc:외화순노출_백만$</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>배당성향</t>
-        </is>
-      </c>
-      <c r="D54" s="24" t="n">
-        <v>0</v>
-      </c>
+          <t>외화순노출_백만$</t>
+        </is>
+      </c>
+      <c r="D54" s="30" t="n"/>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>배당성향(참고 — 모델은 직전 DPS 유지·Q2 지급 가정)</t>
+          <t>외화 순노출 × Δ기말환율 (외화 시트 방식) — 외화 순노출 미공시(face) → 0 + 표기</t>
         </is>
       </c>
       <c r="F54" s="9" t="n"/>
@@ -9541,18 +9316,18 @@
     <row r="55">
       <c r="A55" s="12" t="inlineStr">
         <is>
-          <t>sc:외화순노출_백만$</t>
+          <t>sc:헤지비율</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>외화순노출_백만$</t>
-        </is>
-      </c>
-      <c r="D55" s="30" t="n"/>
+          <t>헤지비율</t>
+        </is>
+      </c>
+      <c r="D55" s="24" t="n"/>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>외화 순노출 × Δ기말환율 (외화 시트 방식) — 외화 순노출 미공시(face) → 0 + 표기</t>
+          <t>sls 없음</t>
         </is>
       </c>
       <c r="F55" s="9" t="n"/>
@@ -9578,15 +9353,15 @@
     <row r="56">
       <c r="A56" s="12" t="inlineStr">
         <is>
-          <t>sc:헤지비율</t>
+          <t>sc:헤지환율_약정</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>헤지비율</t>
-        </is>
-      </c>
-      <c r="D56" s="24" t="n"/>
+          <t>헤지환율_약정</t>
+        </is>
+      </c>
+      <c r="D56" s="16" t="n"/>
       <c r="E56" s="2" t="inlineStr">
         <is>
           <t>sls 없음</t>
@@ -9611,43 +9386,6 @@
       <c r="AM56" s="10" t="n"/>
       <c r="AN56" s="10" t="n"/>
       <c r="AO56" s="11" t="n"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="12" t="inlineStr">
-        <is>
-          <t>sc:헤지환율_약정</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>헤지환율_약정</t>
-        </is>
-      </c>
-      <c r="D57" s="16" t="n"/>
-      <c r="E57" s="2" t="inlineStr">
-        <is>
-          <t>sls 없음</t>
-        </is>
-      </c>
-      <c r="F57" s="9" t="n"/>
-      <c r="K57" s="9" t="n"/>
-      <c r="P57" s="9" t="n"/>
-      <c r="U57" s="9" t="n"/>
-      <c r="Z57" s="9" t="n"/>
-      <c r="AB57" s="5" t="n"/>
-      <c r="AC57" s="10" t="n"/>
-      <c r="AD57" s="10" t="n"/>
-      <c r="AE57" s="11" t="n"/>
-      <c r="AF57" s="10" t="n"/>
-      <c r="AG57" s="10" t="n"/>
-      <c r="AH57" s="10" t="n"/>
-      <c r="AI57" s="10" t="n"/>
-      <c r="AJ57" s="11" t="n"/>
-      <c r="AK57" s="10" t="n"/>
-      <c r="AL57" s="10" t="n"/>
-      <c r="AM57" s="10" t="n"/>
-      <c r="AN57" s="10" t="n"/>
-      <c r="AO57" s="11" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9909,7 +9647,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-08</t>
+          <t>UPDATE: 26-10-09</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -10501,7 +10239,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-08</t>
+          <t>UPDATE: 26-10-09</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -19624,11 +19362,11 @@
         <v/>
       </c>
       <c r="AC12" s="20">
-        <f>IFERROR((AB25*변수!$D$52-AB23*변수!$D$53)/4,"")</f>
+        <f>IFERROR((AB25*변수!$D$51-AB23*변수!$D$52)/4,"")</f>
         <v/>
       </c>
       <c r="AD12" s="20">
-        <f>IFERROR((AC25*변수!$D$52-AC23*변수!$D$53)/4,"")</f>
+        <f>IFERROR((AC25*변수!$D$51-AC23*변수!$D$52)/4,"")</f>
         <v/>
       </c>
       <c r="AE12" s="38">
@@ -19636,19 +19374,19 @@
         <v/>
       </c>
       <c r="AF12" s="20">
-        <f>IFERROR((AD25*변수!$D$52-AD23*변수!$D$53)/4,"")</f>
+        <f>IFERROR((AD25*변수!$D$51-AD23*변수!$D$52)/4,"")</f>
         <v/>
       </c>
       <c r="AG12" s="20">
-        <f>IFERROR((AF25*변수!$D$52-AF23*변수!$D$53)/4,"")</f>
+        <f>IFERROR((AF25*변수!$D$51-AF23*변수!$D$52)/4,"")</f>
         <v/>
       </c>
       <c r="AH12" s="20">
-        <f>IFERROR((AG25*변수!$D$52-AG23*변수!$D$53)/4,"")</f>
+        <f>IFERROR((AG25*변수!$D$51-AG23*변수!$D$52)/4,"")</f>
         <v/>
       </c>
       <c r="AI12" s="20">
-        <f>IFERROR((AH25*변수!$D$52-AH23*변수!$D$53)/4,"")</f>
+        <f>IFERROR((AH25*변수!$D$51-AH23*변수!$D$52)/4,"")</f>
         <v/>
       </c>
       <c r="AJ12" s="38">
@@ -19656,19 +19394,19 @@
         <v/>
       </c>
       <c r="AK12" s="20">
-        <f>IFERROR((AI25*변수!$D$52-AI23*변수!$D$53)/4,"")</f>
+        <f>IFERROR((AI25*변수!$D$51-AI23*변수!$D$52)/4,"")</f>
         <v/>
       </c>
       <c r="AL12" s="20">
-        <f>IFERROR((AK25*변수!$D$52-AK23*변수!$D$53)/4,"")</f>
+        <f>IFERROR((AK25*변수!$D$51-AK23*변수!$D$52)/4,"")</f>
         <v/>
       </c>
       <c r="AM12" s="20">
-        <f>IFERROR((AL25*변수!$D$52-AL23*변수!$D$53)/4,"")</f>
+        <f>IFERROR((AL25*변수!$D$51-AL23*변수!$D$52)/4,"")</f>
         <v/>
       </c>
       <c r="AN12" s="20">
-        <f>IFERROR((AM25*변수!$D$52-AM23*변수!$D$53)/4,"")</f>
+        <f>IFERROR((AM25*변수!$D$51-AM23*변수!$D$52)/4,"")</f>
         <v/>
       </c>
       <c r="AO12" s="38">
@@ -22481,86 +22219,105 @@
           <t>조정 EPS(일회성 의심 분기의 초과 비영업손익 세후 차감 — 모델 추정)</t>
         </is>
       </c>
-      <c r="E31" s="18" t="n">
-        <v>-17.5</v>
+      <c r="E31" s="18">
+        <f>IFERROR(E30,"")</f>
+        <v/>
       </c>
       <c r="F31" s="37" t="n"/>
-      <c r="G31" s="18" t="n">
-        <v>-14.3</v>
-      </c>
-      <c r="H31" s="18" t="n">
-        <v>-35.7</v>
-      </c>
-      <c r="I31" s="18" t="n">
-        <v>-32.7</v>
-      </c>
-      <c r="J31" s="18" t="n">
-        <v>-24.9</v>
+      <c r="G31" s="18">
+        <f>IFERROR(G30,"")</f>
+        <v/>
+      </c>
+      <c r="H31" s="18">
+        <f>IFERROR(H30,"")</f>
+        <v/>
+      </c>
+      <c r="I31" s="18">
+        <f>IFERROR(I30,"")</f>
+        <v/>
+      </c>
+      <c r="J31" s="18">
+        <f>IFERROR(J30,"")</f>
+        <v/>
       </c>
       <c r="K31" s="37">
         <f>SUM(G31:J31)</f>
         <v/>
       </c>
-      <c r="L31" s="18" t="n">
-        <v>29</v>
-      </c>
-      <c r="M31" s="18" t="n">
-        <v>-20.5</v>
-      </c>
-      <c r="N31" s="18" t="n">
-        <v>-59</v>
-      </c>
-      <c r="O31" s="18" t="n">
-        <v>-27.2</v>
+      <c r="L31" s="18">
+        <f>IFERROR(L30,"")</f>
+        <v/>
+      </c>
+      <c r="M31" s="18">
+        <f>IFERROR(M30,"")</f>
+        <v/>
+      </c>
+      <c r="N31" s="18">
+        <f>IFERROR(N30,"")</f>
+        <v/>
+      </c>
+      <c r="O31" s="18">
+        <f>IFERROR(O30,"")</f>
+        <v/>
       </c>
       <c r="P31" s="37">
         <f>SUM(L31:O31)</f>
         <v/>
       </c>
-      <c r="Q31" s="18" t="n">
-        <v>-20</v>
-      </c>
-      <c r="R31" s="18" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="S31" s="18" t="n">
-        <v>-8</v>
-      </c>
-      <c r="T31" s="18" t="n">
-        <v>-22.6</v>
+      <c r="Q31" s="18">
+        <f>IFERROR(Q30,"")</f>
+        <v/>
+      </c>
+      <c r="R31" s="18">
+        <f>IFERROR(R30,"")</f>
+        <v/>
+      </c>
+      <c r="S31" s="18">
+        <f>IFERROR(S30,"")</f>
+        <v/>
+      </c>
+      <c r="T31" s="18">
+        <f>IFERROR(T30,"")</f>
+        <v/>
       </c>
       <c r="U31" s="37">
         <f>SUM(Q31:T31)</f>
         <v/>
       </c>
-      <c r="V31" s="18" t="n">
-        <v>-20.4</v>
-      </c>
-      <c r="W31" s="18" t="n">
-        <v>60.6</v>
-      </c>
-      <c r="X31" s="18" t="n">
-        <v>-3.5</v>
-      </c>
-      <c r="Y31" s="18" t="n">
-        <v>-23.4</v>
+      <c r="V31" s="18">
+        <f>IFERROR(V30,"")</f>
+        <v/>
+      </c>
+      <c r="W31" s="18">
+        <f>IFERROR(W30,"")</f>
+        <v/>
+      </c>
+      <c r="X31" s="18">
+        <f>IFERROR(X30,"")</f>
+        <v/>
+      </c>
+      <c r="Y31" s="18">
+        <f>IFERROR(Y30,"")</f>
+        <v/>
       </c>
       <c r="Z31" s="37">
         <f>SUM(V31:Y31)</f>
         <v/>
       </c>
-      <c r="AA31" s="18" t="n">
-        <v>-25</v>
-      </c>
-      <c r="AB31" s="39" t="n">
-        <v>-63.1</v>
+      <c r="AA31" s="18">
+        <f>IFERROR(AA30,"")</f>
+        <v/>
+      </c>
+      <c r="AB31" s="39">
+        <f>IFERROR((AB18-(19.83)*(1.0))*100/AB29,"")</f>
+        <v/>
       </c>
       <c r="AC31" s="20">
-        <f>IFERROR(X31*(1+변수!AC38),"")</f>
+        <f>IFERROR(AC30,"")</f>
         <v/>
       </c>
       <c r="AD31" s="20">
-        <f>IFERROR(Y31*(1+변수!AD38),"")</f>
+        <f>IFERROR(AD30,"")</f>
         <v/>
       </c>
       <c r="AE31" s="38">
@@ -22568,19 +22325,19 @@
         <v/>
       </c>
       <c r="AF31" s="20">
-        <f>IFERROR(AA31*(1+변수!AF38),"")</f>
+        <f>IFERROR(AF30,"")</f>
         <v/>
       </c>
       <c r="AG31" s="20">
-        <f>IFERROR(AB31*(1+변수!AG38),"")</f>
+        <f>IFERROR(AG30,"")</f>
         <v/>
       </c>
       <c r="AH31" s="20">
-        <f>IFERROR(AC31*(1+변수!AH38),"")</f>
+        <f>IFERROR(AH30,"")</f>
         <v/>
       </c>
       <c r="AI31" s="20">
-        <f>IFERROR(AD31*(1+변수!AI38),"")</f>
+        <f>IFERROR(AI30,"")</f>
         <v/>
       </c>
       <c r="AJ31" s="38">
@@ -22588,19 +22345,19 @@
         <v/>
       </c>
       <c r="AK31" s="20">
-        <f>IFERROR(AF31*(1+변수!AK38),"")</f>
+        <f>IFERROR(AK30,"")</f>
         <v/>
       </c>
       <c r="AL31" s="20">
-        <f>IFERROR(AG31*(1+변수!AL38),"")</f>
+        <f>IFERROR(AL30,"")</f>
         <v/>
       </c>
       <c r="AM31" s="20">
-        <f>IFERROR(AH31*(1+변수!AM38),"")</f>
+        <f>IFERROR(AM30,"")</f>
         <v/>
       </c>
       <c r="AN31" s="20">
-        <f>IFERROR(AI31*(1+변수!AN38),"")</f>
+        <f>IFERROR(AN30,"")</f>
         <v/>
       </c>
       <c r="AO31" s="38">
@@ -22849,7 +22606,7 @@
       <c r="AB33" s="19" t="n"/>
       <c r="AC33" s="20" t="n"/>
       <c r="AD33" s="20">
-        <f>변수!AD39</f>
+        <f>변수!AD38</f>
         <v/>
       </c>
       <c r="AE33" s="38">
@@ -22860,7 +22617,7 @@
       <c r="AG33" s="20" t="n"/>
       <c r="AH33" s="20" t="n"/>
       <c r="AI33" s="20">
-        <f>변수!AI39</f>
+        <f>변수!AI38</f>
         <v/>
       </c>
       <c r="AJ33" s="38">
@@ -22871,7 +22628,7 @@
       <c r="AL33" s="20" t="n"/>
       <c r="AM33" s="20" t="n"/>
       <c r="AN33" s="20">
-        <f>변수!AN39</f>
+        <f>변수!AN38</f>
         <v/>
       </c>
       <c r="AO33" s="38">
@@ -22955,11 +22712,11 @@
         <v/>
       </c>
       <c r="AC34" s="40">
-        <f>IFERROR(변수!$D$42/(Y30+AA30+AB30+AC30),"")</f>
+        <f>IFERROR(변수!$D$41/(Y30+AA30+AB30+AC30),"")</f>
         <v/>
       </c>
       <c r="AD34" s="40">
-        <f>IFERROR(변수!$D$42/(AA30+AB30+AC30+AD30),"")</f>
+        <f>IFERROR(변수!$D$41/(AA30+AB30+AC30+AD30),"")</f>
         <v/>
       </c>
       <c r="AE34" s="41">
@@ -22967,7 +22724,7 @@
         <v/>
       </c>
       <c r="AF34" s="40">
-        <f>IFERROR(변수!$D$42/(AB30+AC30+AD30+AF30),"")</f>
+        <f>IFERROR(변수!$D$41/(AB30+AC30+AD30+AF30),"")</f>
         <v/>
       </c>
       <c r="AG34" s="40" t="n"/>
@@ -23104,11 +22861,11 @@
         <v/>
       </c>
       <c r="AC35" s="40">
-        <f>IFERROR(변수!$D$42/AC32,"")</f>
+        <f>IFERROR(변수!$D$41/AC32,"")</f>
         <v/>
       </c>
       <c r="AD35" s="40">
-        <f>IFERROR(변수!$D$42/AD32,"")</f>
+        <f>IFERROR(변수!$D$41/AD32,"")</f>
         <v/>
       </c>
       <c r="AE35" s="41">
@@ -23116,19 +22873,19 @@
         <v/>
       </c>
       <c r="AF35" s="40">
-        <f>IFERROR(변수!$D$42/AF32,"")</f>
+        <f>IFERROR(변수!$D$41/AF32,"")</f>
         <v/>
       </c>
       <c r="AG35" s="40">
-        <f>IFERROR(변수!$D$42/AG32,"")</f>
+        <f>IFERROR(변수!$D$41/AG32,"")</f>
         <v/>
       </c>
       <c r="AH35" s="40">
-        <f>IFERROR(변수!$D$42/AH32,"")</f>
+        <f>IFERROR(변수!$D$41/AH32,"")</f>
         <v/>
       </c>
       <c r="AI35" s="40">
-        <f>IFERROR(변수!$D$42/AI32,"")</f>
+        <f>IFERROR(변수!$D$41/AI32,"")</f>
         <v/>
       </c>
       <c r="AJ35" s="41">
@@ -23136,19 +22893,19 @@
         <v/>
       </c>
       <c r="AK35" s="40">
-        <f>IFERROR(변수!$D$42/AK32,"")</f>
+        <f>IFERROR(변수!$D$41/AK32,"")</f>
         <v/>
       </c>
       <c r="AL35" s="40">
-        <f>IFERROR(변수!$D$42/AL32,"")</f>
+        <f>IFERROR(변수!$D$41/AL32,"")</f>
         <v/>
       </c>
       <c r="AM35" s="40">
-        <f>IFERROR(변수!$D$42/AM32,"")</f>
+        <f>IFERROR(변수!$D$41/AM32,"")</f>
         <v/>
       </c>
       <c r="AN35" s="40">
-        <f>IFERROR(변수!$D$42/AN32,"")</f>
+        <f>IFERROR(변수!$D$41/AN32,"")</f>
         <v/>
       </c>
       <c r="AO35" s="41">
@@ -24182,7 +23939,7 @@
         </is>
       </c>
       <c r="D2" s="18">
-        <f>변수!D42</f>
+        <f>변수!D41</f>
         <v/>
       </c>
       <c r="W2" s="43" t="n"/>
@@ -29187,7 +28944,7 @@
         </is>
       </c>
       <c r="D2" s="18">
-        <f>변수!D42</f>
+        <f>변수!D41</f>
         <v/>
       </c>
       <c r="I2" s="43" t="n"/>
@@ -30910,7 +30667,7 @@
         </is>
       </c>
       <c r="C1" s="18">
-        <f>변수!D42</f>
+        <f>변수!D41</f>
         <v/>
       </c>
     </row>
@@ -30921,7 +30678,7 @@
         </is>
       </c>
       <c r="C2">
-        <f>변수!D43</f>
+        <f>변수!D42</f>
         <v/>
       </c>
     </row>
@@ -31098,7 +30855,7 @@
         </is>
       </c>
       <c r="D14" s="18">
-        <f>IFERROR(E7*변수!D48+F7*(1-변수!D48),"")</f>
+        <f>IFERROR(E7*변수!D47+F7*(1-변수!D47),"")</f>
         <v/>
       </c>
     </row>
@@ -31109,7 +30866,7 @@
         </is>
       </c>
       <c r="D15" s="27">
-        <f>변수!D45</f>
+        <f>변수!D44</f>
         <v/>
       </c>
       <c r="E15" s="18">
@@ -31133,7 +30890,7 @@
         </is>
       </c>
       <c r="D16" s="27">
-        <f>변수!D46</f>
+        <f>변수!D45</f>
         <v/>
       </c>
       <c r="E16" s="18">
@@ -31157,7 +30914,7 @@
         </is>
       </c>
       <c r="D17" s="27">
-        <f>변수!D47</f>
+        <f>변수!D46</f>
         <v/>
       </c>
       <c r="E17" s="18">
@@ -31221,7 +30978,7 @@
         </is>
       </c>
       <c r="D23" s="21">
-        <f>변수!D44</f>
+        <f>변수!D43</f>
         <v/>
       </c>
     </row>
@@ -33020,7 +32777,7 @@
         </is>
       </c>
       <c r="D16" s="27">
-        <f>변수!D55</f>
+        <f>변수!D54</f>
         <v/>
       </c>
       <c r="E16" s="2" t="inlineStr">

--- a/argus/kship/models/059270_model.xlsx
+++ b/argus/kship/models/059270_model.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="분기" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="TP" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="외화" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
@@ -4976,35 +4976,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1346.2</v>
+        <v>1345.74</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1458.38</v>
+        <v>1457.79</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5095,35 +5095,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5214,35 +5214,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>851.8099999999999</v>
+        <v>851.3099999999999</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>919.9299999999999</v>
+        <v>919.5700000000001</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5333,35 +5333,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5452,35 +5452,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1512.43</v>
+        <v>1510.82</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1691.86</v>
+        <v>1690.9</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5571,35 +5571,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5690,35 +5690,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.79</v>
+        <v>200.73</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.89</v>
+        <v>213.82</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5809,35 +5809,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -5944,7 +5944,7 @@
         <v>5460</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>5170</v>
+        <v>5120</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6217,7 +6217,7 @@
         <v>5525.9</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>5398</v>
+        <v>5388</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -8779,11 +8779,11 @@
         </is>
       </c>
       <c r="D41" s="34" t="n">
-        <v>5170</v>
+        <v>5120</v>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 5,480원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 5,200원)</t>
         </is>
       </c>
       <c r="F41" s="9" t="n"/>
@@ -9093,7 +9093,7 @@
         </is>
       </c>
       <c r="D49" s="36" t="n">
-        <v>0.1901715392654143</v>
+        <v>0.1901715392654144</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -31060,7 +31060,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/059270_model.xlsx
+++ b/argus/kship/models/059270_model.xlsx
@@ -4098,7 +4098,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-09</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-10</t>
         </is>
       </c>
     </row>
@@ -4976,35 +4976,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1345.74</v>
+        <v>1345.14</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1457.79</v>
+        <v>1457.21</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5095,35 +5095,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5214,35 +5214,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>851.3099999999999</v>
+        <v>850.79</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>919.5700000000001</v>
+        <v>919.21</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5333,35 +5333,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5452,35 +5452,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1510.82</v>
+        <v>1509.74</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1690.9</v>
+        <v>1689.95</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5571,35 +5571,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5690,35 +5690,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.73</v>
+        <v>200.69</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.82</v>
+        <v>213.75</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5809,35 +5809,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -9647,7 +9647,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-09</t>
+          <t>UPDATE: 26-10-10</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -10239,7 +10239,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-09</t>
+          <t>UPDATE: 26-10-10</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/059270_model.xlsx
+++ b/argus/kship/models/059270_model.xlsx
@@ -4098,7 +4098,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-10</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-11</t>
         </is>
       </c>
     </row>
@@ -9647,7 +9647,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-10</t>
+          <t>UPDATE: 26-10-11</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -10239,7 +10239,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-10</t>
+          <t>UPDATE: 26-10-11</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/059270_model.xlsx
+++ b/argus/kship/models/059270_model.xlsx
@@ -4098,7 +4098,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-11</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-12</t>
         </is>
       </c>
     </row>
@@ -5944,7 +5944,7 @@
         <v>5460</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>5120</v>
+        <v>4805</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6126,7 +6126,7 @@
         <v>3980</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>5050</v>
+        <v>4800</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -6217,7 +6217,7 @@
         <v>5525.9</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>5388</v>
+        <v>5290.8</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -8779,7 +8779,7 @@
         </is>
       </c>
       <c r="D41" s="34" t="n">
-        <v>5120</v>
+        <v>4805</v>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
@@ -8819,7 +8819,7 @@
       </c>
       <c r="D42" s="35" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -9647,7 +9647,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-11</t>
+          <t>UPDATE: 26-10-12</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -10239,7 +10239,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-11</t>
+          <t>UPDATE: 26-10-12</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -23952,7 +23952,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -28957,7 +28957,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -31060,7 +31060,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1.41</v>
+        <v>1.32</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/059270_model.xlsx
+++ b/argus/kship/models/059270_model.xlsx
@@ -4098,7 +4098,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-12</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-13</t>
         </is>
       </c>
     </row>
@@ -4976,35 +4976,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1345.14</v>
+        <v>1343.63</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1457.21</v>
+        <v>1456.58</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5095,35 +5095,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5214,35 +5214,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>850.79</v>
+        <v>849.51</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>919.21</v>
+        <v>918.8099999999999</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5333,35 +5333,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5452,35 +5452,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1509.74</v>
+        <v>1507.34</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1689.95</v>
+        <v>1688.95</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5571,35 +5571,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5690,35 +5690,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.69</v>
+        <v>200.5</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.75</v>
+        <v>213.68</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5809,35 +5809,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -5944,7 +5944,7 @@
         <v>5460</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>4805</v>
+        <v>4740</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6126,7 +6126,7 @@
         <v>3980</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>4800</v>
+        <v>4550</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -6217,7 +6217,7 @@
         <v>5525.9</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>5290.8</v>
+        <v>5212.1</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -8779,11 +8779,11 @@
         </is>
       </c>
       <c r="D41" s="34" t="n">
-        <v>4805</v>
+        <v>4740</v>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 5,200원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 5,140원)</t>
         </is>
       </c>
       <c r="F41" s="9" t="n"/>
@@ -8819,7 +8819,7 @@
       </c>
       <c r="D42" s="35" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -9647,7 +9647,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-12</t>
+          <t>UPDATE: 26-10-13</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -10239,7 +10239,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-12</t>
+          <t>UPDATE: 26-10-13</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -23952,7 +23952,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -28957,7 +28957,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -31060,7 +31060,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/059270_model.xlsx
+++ b/argus/kship/models/059270_model.xlsx
@@ -4098,7 +4098,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-13</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-14</t>
         </is>
       </c>
     </row>
@@ -4976,35 +4976,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1343.63</v>
+        <v>1343.39</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1456.58</v>
+        <v>1456.01</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5095,35 +5095,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5214,35 +5214,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>849.51</v>
+        <v>849.39</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>918.8099999999999</v>
+        <v>918.46</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5333,35 +5333,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5452,35 +5452,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1507.34</v>
+        <v>1506.62</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1688.95</v>
+        <v>1688.01</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5571,35 +5571,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5690,35 +5690,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.5</v>
+        <v>200.49</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.68</v>
+        <v>213.61</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5809,35 +5809,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6217,7 +6217,7 @@
         <v>5525.9</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>5212.1</v>
+        <v>5165</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -8783,7 +8783,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 5,140원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 4,840원)</t>
         </is>
       </c>
       <c r="F41" s="9" t="n"/>
@@ -8819,7 +8819,7 @@
       </c>
       <c r="D42" s="35" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -9647,7 +9647,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-13</t>
+          <t>UPDATE: 26-10-14</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -10239,7 +10239,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-13</t>
+          <t>UPDATE: 26-10-14</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -23952,7 +23952,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -28957,7 +28957,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/059270_model.xlsx
+++ b/argus/kship/models/059270_model.xlsx
@@ -4098,7 +4098,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-14</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-19</t>
         </is>
       </c>
     </row>
@@ -4976,35 +4976,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1343.39</v>
+        <v>1342.11</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1456.01</v>
+        <v>1454.27</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5095,35 +5095,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5214,35 +5214,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>849.39</v>
+        <v>848.59</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>918.46</v>
+        <v>917.39</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5333,35 +5333,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5452,35 +5452,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1506.62</v>
+        <v>1505.3</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1688.01</v>
+        <v>1685.25</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5571,35 +5571,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5690,35 +5690,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.49</v>
+        <v>200.38</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.61</v>
+        <v>213.41</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5809,35 +5809,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -5944,7 +5944,7 @@
         <v>5460</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>4740</v>
+        <v>4860</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6126,7 +6126,7 @@
         <v>3980</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>4550</v>
+        <v>4410</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -6217,7 +6217,7 @@
         <v>5525.9</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>5165</v>
+        <v>5065.9</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -8779,11 +8779,11 @@
         </is>
       </c>
       <c r="D41" s="34" t="n">
-        <v>4740</v>
+        <v>4860</v>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 4,840원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 4,530원)</t>
         </is>
       </c>
       <c r="F41" s="9" t="n"/>
@@ -8819,7 +8819,7 @@
       </c>
       <c r="D42" s="35" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -9647,7 +9647,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-14</t>
+          <t>UPDATE: 26-10-19</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -10239,7 +10239,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-14</t>
+          <t>UPDATE: 26-10-19</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -23952,7 +23952,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -28957,7 +28957,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -31060,7 +31060,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/059270_model.xlsx
+++ b/argus/kship/models/059270_model.xlsx
@@ -4098,7 +4098,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-19</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-26</t>
         </is>
       </c>
     </row>
@@ -4976,35 +4976,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1342.11</v>
+        <v>1337.49</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1454.27</v>
+        <v>1451.19</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5095,35 +5095,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5214,35 +5214,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>848.59</v>
+        <v>846.51</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>917.39</v>
+        <v>915.5700000000001</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5333,35 +5333,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5452,35 +5452,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1505.3</v>
+        <v>1500.06</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1685.25</v>
+        <v>1680.5</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5571,35 +5571,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5690,35 +5690,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.38</v>
+        <v>199.88</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.41</v>
+        <v>213.06</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5809,35 +5809,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -5944,7 +5944,7 @@
         <v>5460</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>4860</v>
+        <v>4630</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6217,7 +6217,7 @@
         <v>5525.9</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>5065.9</v>
+        <v>4945.9</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -8779,11 +8779,11 @@
         </is>
       </c>
       <c r="D41" s="34" t="n">
-        <v>4860</v>
+        <v>4630</v>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 4,530원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 4,655원)</t>
         </is>
       </c>
       <c r="F41" s="9" t="n"/>
@@ -8819,7 +8819,7 @@
       </c>
       <c r="D42" s="35" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -9647,7 +9647,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-19</t>
+          <t>UPDATE: 26-10-26</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -10239,7 +10239,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-19</t>
+          <t>UPDATE: 26-10-26</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -23952,7 +23952,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -28957,7 +28957,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -31060,7 +31060,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
     </row>
     <row r="33">
